--- a/hardware/PurchaseRequest_FH02_2_17_2026.xlsx
+++ b/hardware/PurchaseRequest_FH02_2_17_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashto\Dev\SeniorDesign_SwanGanz\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1FFE51-E2CB-46EE-BE1F-8258A4A2E405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166CF364-92CD-4075-81CE-78BCD4BC5E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>Your Name</t>
   </si>
@@ -206,79 +206,82 @@
     <t>Shopping Cart Link:</t>
   </si>
   <si>
-    <t>https://www.mouser.com/Tools/SavedCart/Share?AccessID=e14d5008ca</t>
-  </si>
-  <si>
     <t>https://www.mouser.com/</t>
   </si>
   <si>
-    <t>GRT31C5C1E104FA02L</t>
-  </si>
-  <si>
-    <t>SQ2389CES-T1_GE3</t>
-  </si>
-  <si>
-    <t>CRCW060347K0FKED</t>
-  </si>
-  <si>
-    <t>RCA060310K0FKEC</t>
-  </si>
-  <si>
-    <t>TNPW06031K00FHEA</t>
-  </si>
-  <si>
-    <t>1879246-3</t>
-  </si>
-  <si>
-    <t>RCA0603100KFKEC</t>
-  </si>
-  <si>
-    <t>AC0603FRE07100RL</t>
-  </si>
-  <si>
-    <t>CR0603-FX-8201ELF</t>
-  </si>
-  <si>
-    <t>RT0603DRD0765K5L</t>
-  </si>
-  <si>
-    <t>RT0603DRE07160KL</t>
-  </si>
-  <si>
-    <t>RC0603FR-10200RL</t>
-  </si>
-  <si>
-    <t>RN73R1JTTD3202F50</t>
-  </si>
-  <si>
-    <t>CRCW060317K4FKEAC</t>
-  </si>
-  <si>
-    <t>INA122UA/2K5</t>
-  </si>
-  <si>
-    <t>CR0603-FX-5101ELF</t>
-  </si>
-  <si>
     <t>ea</t>
   </si>
   <si>
     <t>Estimated Tariff</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1590 / Adafruit - LCD Driver</t>
-  </si>
-  <si>
-    <t>1596 / Adafruit - LCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1206C106J3RACTU / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC0603JRX7R9BB104 </t>
-  </si>
-  <si>
     <t>Total :</t>
+  </si>
+  <si>
+    <t>CC0603JRX7R9BB104 - https://mou.sr/3KIvj2i</t>
+  </si>
+  <si>
+    <t>C1206C106J3RACTU - https://mou.sr/4aW77nK</t>
+  </si>
+  <si>
+    <t>GRT31C5C1E104FA02L - https://mou.sr/49WiPhJ</t>
+  </si>
+  <si>
+    <t>SQ2389CES-T1_GE3 - https://mou.sr/4rGY4NL</t>
+  </si>
+  <si>
+    <t>CRCW060347K0FKED - https://mou.sr/43XqsSa</t>
+  </si>
+  <si>
+    <t>RCA060310K0FKEC - https://mou.sr/463dpQf</t>
+  </si>
+  <si>
+    <t>TNPW06031K00FHEA - https://mou.sr/463dpQf</t>
+  </si>
+  <si>
+    <t>1879246-3 - https://mou.sr/4cx5VIG</t>
+  </si>
+  <si>
+    <t>RCA0603100KFKEC - https://mou.sr/4cx5VIG</t>
+  </si>
+  <si>
+    <t>AC0603FRE07100RL - https://mou.sr/4c1KKys</t>
+  </si>
+  <si>
+    <t>CR0603-FX-8201ELF - https://mou.sr/4qIgw7c</t>
+  </si>
+  <si>
+    <t>RT0603DRD0765K5L - https://mou.sr/3MPLMDg</t>
+  </si>
+  <si>
+    <t>RT0603DRE07160KL - https://mou.sr/4rTJm5k</t>
+  </si>
+  <si>
+    <t>RC0603FR-10200RL - https://mou.sr/3ZHKSvC</t>
+  </si>
+  <si>
+    <t>RN73R1JTTD3202F50 - https://mou.sr/3Okpha6</t>
+  </si>
+  <si>
+    <t>CRCW060317K4FKEAC - https://mou.sr/4rW5MTx</t>
+  </si>
+  <si>
+    <t>INA122UA/2K5 - https://mou.sr/4rlVpsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1590 / Adafruit - LCD Driver - https://mou.sr/3flqagV</t>
+  </si>
+  <si>
+    <t>1596 / Adafruit - LCD - https://mou.sr/3NU5UAa</t>
+  </si>
+  <si>
+    <t>CR0603-FX-5101ELF - https://mou.sr/4aBpv3T</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/Tools/SavedCart/Share?AccessID=481e90da45</t>
+  </si>
+  <si>
+    <t>Total Merchandise:</t>
   </si>
 </sst>
 </file>
@@ -289,7 +292,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -395,14 +398,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF0070BB"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -568,7 +563,7 @@
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -592,16 +587,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="16" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="15" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="16" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="15" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="16"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="Currency" xfId="15" builtinId="4"/>
@@ -957,14 +951,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
     <col min="2" max="2" width="44.33203125" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -989,55 +983,55 @@
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="5">
         <v>8324958905</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>46070</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="5"/>
@@ -1068,33 +1062,33 @@
       <c r="A13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="22"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="23"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="6"/>
       <c r="C14" s="30" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="23"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
@@ -1108,8 +1102,8 @@
       <c r="A18" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>30</v>
+      <c r="B18" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1147,18 +1141,18 @@
         <v>1</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5">
         <v>50</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="24">
         <f>C22*E22</f>
         <v>1.7500000000000002</v>
       </c>
@@ -1169,18 +1163,18 @@
         <v>2</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5">
         <v>10</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E23" s="5">
         <v>0.626</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="24">
         <f t="shared" ref="F23:F41" si="0">C23*E23</f>
         <v>6.26</v>
       </c>
@@ -1191,18 +1185,18 @@
         <v>3</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5">
         <v>10</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E24" s="5">
         <v>0.44700000000000001</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="24">
         <f t="shared" si="0"/>
         <v>4.47</v>
       </c>
@@ -1213,18 +1207,18 @@
         <v>4</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C25" s="5">
         <v>10</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E25" s="5">
         <v>0.42099999999999999</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="24">
         <f t="shared" si="0"/>
         <v>4.21</v>
       </c>
@@ -1235,18 +1229,18 @@
         <v>5</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C26" s="5">
         <v>10</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E26" s="5">
         <v>6.3E-2</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="24">
         <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
@@ -1257,18 +1251,18 @@
         <v>6</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>50</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E27" s="5">
         <v>0.06</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1279,18 +1273,18 @@
         <v>7</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C28" s="5">
         <v>10</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E28" s="5">
         <v>7.8E-2</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="24">
         <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
@@ -1301,18 +1295,18 @@
         <v>8</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C29" s="5">
         <v>25</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E29" s="5">
         <v>0.16200000000000001</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="24">
         <f t="shared" si="0"/>
         <v>4.05</v>
       </c>
@@ -1323,20 +1317,20 @@
         <v>9</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C30" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E30" s="5">
         <v>0.06</v>
       </c>
-      <c r="F30" s="27">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="F30" s="24">
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="G30" s="9"/>
     </row>
@@ -1345,18 +1339,18 @@
         <v>10</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C31" s="5">
         <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E31" s="5">
         <v>0.02</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="24">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
@@ -1367,18 +1361,18 @@
         <v>11</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C32" s="5">
         <v>10</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E32" s="5">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="24">
         <f t="shared" si="0"/>
         <v>0.10999999999999999</v>
       </c>
@@ -1389,207 +1383,216 @@
         <v>12</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C33" s="5">
         <v>10</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E33" s="5">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="24">
         <f t="shared" si="0"/>
         <v>0.32</v>
       </c>
       <c r="G33" s="9"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="28">
+      <c r="A34" s="5">
         <v>13</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="28">
+        <v>45</v>
+      </c>
+      <c r="C34" s="5">
         <v>20</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F34" s="24">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="5">
+        <v>20</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F35" s="24">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
+        <v>15</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="28">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F34" s="27">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="28">
-        <v>14</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="28">
+      <c r="C36" s="5">
+        <v>25</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="5">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="F36" s="24">
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
+        <v>16</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="5">
         <v>20</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="28">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F35" s="27">
-        <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="28">
-        <v>15</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="28">
-        <v>25</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="28">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="F36" s="27">
-        <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="28">
-        <v>16</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="28">
+      <c r="D37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="F37" s="24">
+        <f t="shared" si="0"/>
+        <v>1.1600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="5">
+        <v>17</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="5">
+        <v>5.17</v>
+      </c>
+      <c r="F38" s="24">
+        <f t="shared" si="0"/>
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
+        <v>18</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="5">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="F39" s="24">
+        <f t="shared" si="0"/>
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="5">
+        <v>19</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="5">
+        <v>2</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="5">
+        <v>29.95</v>
+      </c>
+      <c r="F40" s="24">
+        <f t="shared" si="0"/>
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
         <v>20</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="28">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="F37" s="27">
-        <f t="shared" si="0"/>
-        <v>1.1600000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="28">
-        <v>17</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="28">
-        <v>10</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="28">
-        <v>5.17</v>
-      </c>
-      <c r="F38" s="27">
-        <f t="shared" si="0"/>
-        <v>51.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="28">
-        <v>18</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="28">
-        <v>2</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="28">
-        <v>39.950000000000003</v>
-      </c>
-      <c r="F39" s="27">
-        <f t="shared" si="0"/>
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="28">
-        <v>19</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="28">
-        <v>2</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="28">
-        <v>29.95</v>
-      </c>
-      <c r="F40" s="27">
-        <f t="shared" si="0"/>
-        <v>59.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="28">
+      <c r="B41" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="5">
         <v>20</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="28">
-        <v>20</v>
-      </c>
       <c r="D41" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="28">
+        <v>30</v>
+      </c>
+      <c r="E41" s="5">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="24">
         <f t="shared" si="0"/>
         <v>0.21999999999999997</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E42" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="32">
+        <v>31</v>
+      </c>
+      <c r="F42" s="26">
         <v>4.95</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E43" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F43" s="27">
-        <f>SUM(F22:F42)</f>
-        <v>229.05</v>
+        <v>54</v>
+      </c>
+      <c r="F43" s="24">
+        <f>SUM(F22:F41)</f>
+        <v>222.90000000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E44" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="31">
+        <f>SUM(F42:F43)</f>
+        <v>227.85000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1605,9 +1608,10 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{34D611E8-6A26-4C37-800D-626CE00089E5}"/>
+    <hyperlink ref="C14" r:id="rId2" xr:uid="{A0FB1489-4766-4FDB-8D21-D45BDF988BBD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.5" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId2"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId3"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
